--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_uk_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_uk_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>18-11-2021 08:30</t>
+          <t>2021-11-18 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>26-01-2021 08:30</t>
+          <t>2021-01-26 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>25-06-2021 08:30</t>
+          <t>2021-06-25 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>25-06-2021 08:30</t>
+          <t>2021-06-25 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>25-06-2021 08:30</t>
+          <t>2021-06-25 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>25-06-2021 08:30</t>
+          <t>2021-06-25 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>25-06-2021 08:30</t>
+          <t>2021-06-25 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10160,7 +10160,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>18-11-2021 08:30</t>
+          <t>2021-11-18 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13344,7 +13344,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13437,7 +13437,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="inlineStr"/>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr"/>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr"/>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -13995,7 +13995,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -14088,7 +14088,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr"/>
@@ -14181,7 +14181,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr"/>
@@ -14367,7 +14367,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr"/>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="inlineStr"/>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="inlineStr"/>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr"/>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr"/>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>29-05-2021 08:30</t>
+          <t>2021-05-29 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16441,7 +16441,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>29-05-2021 08:30</t>
+          <t>2021-05-29 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17106,7 +17106,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17391,7 +17391,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>29-05-2021 08:30</t>
+          <t>2021-05-29 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18151,7 +18151,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -18717,7 +18717,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
@@ -18996,7 +18996,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -19089,7 +19089,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
